--- a/doc/Првки операции предъявления.xlsx
+++ b/doc/Првки операции предъявления.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\IDS_RailWay_Core\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{094FE86B-9927-438A-9D83-2F7A0C28E888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DBD3B0-DAE0-48D5-8132-974318AD2E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B214B4B8-9D79-46C4-85B9-6DE4894AC0ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Предъявление" sheetId="1" r:id="rId1"/>
-    <sheet name="Дислокация" sheetId="2" r:id="rId2"/>
-    <sheet name="Роспуск" sheetId="3" r:id="rId3"/>
+    <sheet name="Аркуш1" sheetId="4" r:id="rId2"/>
+    <sheet name="Дислокация" sheetId="2" r:id="rId3"/>
+    <sheet name="Роспуск" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -105,7 +106,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -115,6 +116,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -131,16 +144,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -168,8 +187,8 @@
       <xdr:rowOff>76201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>52777</xdr:rowOff>
     </xdr:to>
@@ -243,7 +262,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:colOff>95250</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>154249</xdr:rowOff>
     </xdr:to>
@@ -434,8 +453,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
@@ -1054,6 +1073,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D460B537-D447-43D9-B0A3-B0E7B621A00A}">
   <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
@@ -1061,27 +1083,27 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1093,6 +1115,70 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871BE70C-9D17-4E7E-8C97-96614313A792}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>61823415</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>63312110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>52321296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>63029565</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>63361166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>60508223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>63190037</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>63195838</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>62253026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>61551131</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D7D695-149E-4FB8-B3BF-5A0AAC5952C8}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1113,7 +1199,7 @@
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1123,7 +1209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{383DAE17-FF5E-426E-95EB-F57263893B7B}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/doc/Првки операции предъявления.xlsx
+++ b/doc/Првки операции предъявления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\IDS_RailWay_Core\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DBD3B0-DAE0-48D5-8132-974318AD2E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779BFFA9-6C5C-4C8D-8420-314C25FD8317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B214B4B8-9D79-46C4-85B9-6DE4894AC0ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B214B4B8-9D79-46C4-85B9-6DE4894AC0ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Предъявление" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,6 +131,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -144,13 +150,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -160,6 +165,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -1083,27 +1090,27 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1189,17 +1196,17 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
     </row>

--- a/doc/Првки операции предъявления.xlsx
+++ b/doc/Првки операции предъявления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\IDS_RailWay_Core\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779BFFA9-6C5C-4C8D-8420-314C25FD8317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75639355-9B1F-4D71-A297-1C8BD2EE6FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B214B4B8-9D79-46C4-85B9-6DE4894AC0ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B214B4B8-9D79-46C4-85B9-6DE4894AC0ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Предъявление" sheetId="1" r:id="rId1"/>
@@ -152,9 +152,6 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -167,6 +164,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -1085,32 +1083,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1191,22 +1189,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1222,17 +1220,17 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
